--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -525,7 +525,7 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="1">
-    <x:tablePart r:id="rId1"/>
+    <x:tablePart r:id="rId5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -65,7 +65,14 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -436,10 +436,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.410625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.550625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.700625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8.090625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.860625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.1706250000000011" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.830625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -109,19 +109,19 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -438,7 +438,7 @@
   <x:cols>
     <x:col min="1" max="1" width="8.090625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.860625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.1706250000000011" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.170625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.830625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
